--- a/research/v21-seeded-documents/packs/retail-price-accuracy/or/documents/evidence-register.xlsx
+++ b/research/v21-seeded-documents/packs/retail-price-accuracy/or/documents/evidence-register.xlsx
@@ -719,7 +719,7 @@
       </c>
       <c r="B2" s="4" t="inlineStr">
         <is>
-          <t>checkout control gap mapped to Or. Rev. Stat. §§ 616.850–616.890</t>
+          <t>checkout control gap mapped to OAR 603-027-0180; Or. Rev. Stat. §§ 616.850–616.890</t>
         </is>
       </c>
       <c r="C2" s="3" t="n">
@@ -906,7 +906,7 @@
       </c>
       <c r="B8" s="2" t="inlineStr">
         <is>
-          <t>Or. Rev. Stat. §§ 616.850–616.890</t>
+          <t>OAR 603-027-0180; Or. Rev. Stat. §§ 616.850–616.890</t>
         </is>
       </c>
     </row>
@@ -918,7 +918,7 @@
       </c>
       <c r="B9" s="2" t="inlineStr">
         <is>
-          <t>https://www.oregonlegislature.gov/bills_laws/ors/ors616.html</t>
+          <t>https://secure.sos.state.or.us/oard/view.action?ruleNumber=603-027-0180</t>
         </is>
       </c>
     </row>
